--- a/doctool/test/auto/scenario32/システム機能設計書_サンプル_S32.xlsx
+++ b/doctool/test/auto/scenario32/システム機能設計書_サンプル_S32.xlsx
@@ -2245,7 +2245,24 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>山田　太郎</author>
+  </authors>
+  <commentList>
+    <comment ref="E35" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:g
+gカテゴリの指摘コメント。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
     <author>作成者</author>
+    <author>山田　太郎</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -2281,6 +2298,24 @@
 最後の行に「済」と書くと指摘をクローズできる。
 「済」の前にスペースを空けて確認日と確認者を書くこともできる。
 08/02山田 済</t>
+      </text>
+    </comment>
+    <comment ref="E63" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:d
+機能・仕様誤りの指摘例（カテゴリd）。</t>
+      </text>
+    </comment>
+    <comment ref="E64" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:e
+設計・ドキュメント規約違反の指摘例（カテゴリe）。</t>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:f
+記述誤りの指摘例（カテゴリf）。</t>
       </text>
     </comment>
     <comment ref="A71" authorId="0" shapeId="0">
@@ -3354,7 +3389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="4.83203125" defaultRowHeight="11.25"/>
   <sheetData>
     <row r="1" customFormat="1" s="11">
@@ -4798,6 +4833,9 @@
       <c r="AI33" s="366" t="n"/>
     </row>
     <row r="34" ht="15" customFormat="1" customHeight="1" s="39"/>
+    <row r="35">
+      <c r="E35" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="179">
     <mergeCell ref="D11:F11"/>
@@ -4983,6 +5021,7 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -16591,7 +16630,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="E65" t="inlineStr">
         <is>
@@ -16599,7 +16637,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="70">
       <c r="A70" s="94" t="n"/>
     </row>

--- a/doctool/test/auto/scenario32/システム機能設計書_サンプル_S32.xlsx
+++ b/doctool/test/auto/scenario32/システム機能設計書_サンプル_S32.xlsx
@@ -2248,10 +2248,22 @@
     <author>山田　太郎</author>
   </authors>
   <commentList>
-    <comment ref="E35" authorId="0" shapeId="0">
+    <comment ref="E65" authorId="0" shapeId="0">
       <text>
-        <t>山田　太郎:g
-gカテゴリの指摘コメント。</t>
+        <t>山田　太郎:m
+mカテゴリの指摘コメント。</t>
+      </text>
+    </comment>
+    <comment ref="E70" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:n
+nカテゴリの指摘コメント。</t>
+      </text>
+    </comment>
+    <comment ref="E75" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:o
+oカテゴリの指摘コメント。</t>
       </text>
     </comment>
   </commentList>
@@ -2318,10 +2330,46 @@
 記述誤りの指摘例（カテゴリf）。</t>
       </text>
     </comment>
+    <comment ref="E66" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:g
+疑問点・確認の指摘例（カテゴリg）。</t>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:h
+改善要望の指摘例（カテゴリh）。</t>
+      </text>
+    </comment>
+    <comment ref="E68" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:i
+仕様変更の指摘例（カテゴリi）。</t>
+      </text>
+    </comment>
+    <comment ref="E69" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:j
+テスト項目漏れの指摘例（カテゴリj）。</t>
+      </text>
+    </comment>
+    <comment ref="E70" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:k
+テスト漏れの指摘例（カテゴリk）。</t>
+      </text>
+    </comment>
     <comment ref="A71" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:
 自動で挿入される名前とコロンの直後に何も書かれていない場合、日時コメント・指摘コメントとして扱われない。</t>
+      </text>
+    </comment>
+    <comment ref="E71" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:l
+その他の指摘例（カテゴリl）。</t>
       </text>
     </comment>
   </commentList>
@@ -3389,7 +3437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="4.83203125" defaultRowHeight="11.25"/>
   <sheetData>
     <row r="1" customFormat="1" s="11">
@@ -4833,8 +4881,14 @@
       <c r="AI33" s="366" t="n"/>
     </row>
     <row r="34" ht="15" customFormat="1" customHeight="1" s="39"/>
-    <row r="35">
-      <c r="E35" t="n"/>
+    <row r="65">
+      <c r="E65" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" t="n"/>
+    </row>
+    <row r="75">
+      <c r="E75" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="179">
